--- a/AAII_Financials/Quarterly/BEKE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BEKE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="92">
   <si>
     <t>BEKE</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3612600</v>
+      </c>
+      <c r="E8" s="3">
         <v>2739000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3172400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3238100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3630800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3214800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4264200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3219700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3216000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2268200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2849300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2441000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2686600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2952000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2361000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2431100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1915300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1744400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2455800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2572400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3471800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2972500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3155700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3028100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4017200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1123200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2214500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1875700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1749500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1246700</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2580000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2077900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2492300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2544900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2835200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2550500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3281900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2487700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2319200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1697300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2123900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1772000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1949800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2027600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1784000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1773600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1538800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1435800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2053300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2180800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2705900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2280800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2400700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2382200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3897200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1044100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1791400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1417100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1217700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>925800</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1032500</v>
+      </c>
+      <c r="E10" s="3">
         <v>661100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>680000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>693200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>795600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>664400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>982300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>732000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>896800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>570900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>725400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>668900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>736800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>924400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>577000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>657600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>376500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>308600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>402500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>391600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>765900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>691700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>755000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>645900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>120000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>79100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>423100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>458600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>531800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>320800</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E12" s="3">
         <v>71400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>102300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>91100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>88400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>80400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>101200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>81700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>69400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>64700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>75300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>64600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>65500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>66500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>71700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>70400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>108200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>104100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>101900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>148200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>111300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>91600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>99400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>116300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>143600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>71100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>73600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>68000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>52700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>47700</v>
       </c>
-      <c r="AG12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,80 +1338,83 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-19600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-86300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-11500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-15200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-94300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-15500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-4400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-123800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>24200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>33300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>41600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>73700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>56400</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3">
         <v>32900</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1407,8 +1427,8 @@
       <c r="AD14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
@@ -1419,53 +1439,56 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E15" s="3">
         <v>29200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>50800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>40100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>30400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>29400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>37900</v>
-      </c>
-      <c r="J15" s="3">
-        <v>28900</v>
       </c>
       <c r="K15" s="3">
         <v>28900</v>
       </c>
       <c r="L15" s="3">
+        <v>28900</v>
+      </c>
+      <c r="M15" s="3">
         <v>44800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>50000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>48300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>48500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>49900</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,193 +1576,197 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3167100</v>
+      </c>
+      <c r="E17" s="3">
         <v>2554500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3192900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3140800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3479000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3133400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4109900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3116100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2933700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2266500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2865900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2315400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2533000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2518500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2320500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2296500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2157400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1875900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2644700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2899300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3311600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2827000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2979400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3040000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3773200</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE17" s="3">
         <v>1813300</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG17" s="3">
-        <v>0</v>
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>445500</v>
+      </c>
+      <c r="E18" s="3">
         <v>184500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-20500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>97300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>151800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>81400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>154300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>103600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>282300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-16600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>125600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>153600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>433500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>40500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>134700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-242100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-131500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-188900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-326900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>160200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>145500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>176300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-11900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>244000</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE18" s="3">
         <v>62400</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1746,8 +1776,11 @@
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,95 +1815,96 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-50700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-41900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>48500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-56200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-45300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-56900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>69000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-74900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-42500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-71400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>45300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-57400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-18000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-86700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>25000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>42700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>71500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>97200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>104800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>110400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>67400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>76000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>61200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>92000</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE20" s="3">
         <v>47100</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1880,86 +1914,89 @@
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>523900</v>
+      </c>
+      <c r="E21" s="3">
         <v>255600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-18200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>193500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>227500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>167700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>123200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>207400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>353700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>117900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-11800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>231400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>220100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>570100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>143600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>158100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-195200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-10700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-83900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-220400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>277000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>254500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>373400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>13900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>416200</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1978,52 +2015,55 @@
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
         <v>1000</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
         <v>1700</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
         <v>2400</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2034,8 +2074,8 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
@@ -2052,12 +2092,12 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB22" s="3">
         <v>5900</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
       <c r="AC22" s="3">
         <v>0</v>
       </c>
@@ -2076,204 +2116,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>526000</v>
+      </c>
+      <c r="E23" s="3">
         <v>265600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>39900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>182200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>239800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>190600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>220600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>238300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>378300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>116200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>107400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>229100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>216900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>564500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>141400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>159700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-199400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-60000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-91700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-222100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>270600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>212900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>252300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>49300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>330100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-217700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-479900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>109400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>134900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>39200</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>139700</v>
+      </c>
+      <c r="E24" s="3">
         <v>83600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>28100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>77300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>57400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>72700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>141500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>71700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>116800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>56300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>12900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>68700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>37700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>164200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>88900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>60700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>60000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>26100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>37200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>28900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>110400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>60800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>99800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>38200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>93300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-23500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>49500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>75100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>13900</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>386300</v>
+      </c>
+      <c r="E26" s="3">
         <v>182000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>11800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>104900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>182400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>117900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>79100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>166600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>261500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>59800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>94500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>160400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>179200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>400300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>52400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>98900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-259400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-86100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-128900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-251000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>160200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>152100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>152500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>11100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>236900</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE26" s="3">
         <v>59900</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG26" s="3">
-        <v>0</v>
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>386100</v>
+      </c>
+      <c r="E27" s="3">
         <v>182000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>105200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>181600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>117900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>78100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>167000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>260400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>59800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>94400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>158700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>180500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>399900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>53200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>99900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-259700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-85900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-128400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-250900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>159700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>152000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>110400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-40000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>14500</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-11900</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG27" s="3">
-        <v>0</v>
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,95 +3025,98 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>50700</v>
+      </c>
+      <c r="E32" s="3">
         <v>41900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-48500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>56200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>45300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>56900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-69000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>74900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>42500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>71400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-45300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>57400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>18000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>86700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-25000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-42700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-71500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-97200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-104800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-110400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-67400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-76000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-61200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-92000</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-47100</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
@@ -3056,106 +3126,112 @@
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>386100</v>
+      </c>
+      <c r="E33" s="3">
         <v>182000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>105200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>181600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>117900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>78100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>167000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>260400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>59800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>94400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>158700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>180500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>399900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>53200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>99900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-259700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-85900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-128400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-250900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>159700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>152000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>110400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-40000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>14500</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-11900</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG33" s="3">
-        <v>0</v>
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>386100</v>
+      </c>
+      <c r="E35" s="3">
         <v>182000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>105200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>181600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>117900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>78100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>167000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>260400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>59800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>94400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>158700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>180500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>399900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>53200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>99900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-259700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-85900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-128400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-250900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>159700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>152000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>110400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-40000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>14500</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-11900</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG35" s="3">
-        <v>0</v>
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,86 +3611,87 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1087500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1605600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1111300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1295300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1551700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1760200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1567700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1365300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1294800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2471500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2769000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2170700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4377900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4453900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2736900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2618600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1720900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2304800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2823200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3096100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4386800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3860400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5703000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5606500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3695700</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,86 +3710,89 @@
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5827600</v>
+      </c>
+      <c r="E42" s="3">
         <v>4916500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5658800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5585700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4727100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4392900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5660700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6223400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5810300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4990600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4831300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5263800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3164800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>4096600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>5002800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>4519700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>4259400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3729600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>4059900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>3318400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2568100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3189100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2183800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1938800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>864900</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3721,86 +3811,89 @@
       <c r="AH42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1168800</v>
+      </c>
+      <c r="E43" s="3">
         <v>960300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>866200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>735400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>985300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1074400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1204400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>638300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>799400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>655900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>715700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>480000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>645200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>861400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>745300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>777500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>925000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1122700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1472100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1956200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2693900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2554800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2553400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1902500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1990900</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3819,52 +3912,55 @@
       <c r="AH43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>418300</v>
+      </c>
+      <c r="E44" s="3">
         <v>406100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>408000</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3">
         <v>220600</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3">
         <v>42900</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3917,86 +4013,89 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>523200</v>
+      </c>
+      <c r="E45" s="3">
         <v>546600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>361600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1047700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1061400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1043700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>415200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>816400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>701700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>691000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>371500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>722000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>652100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>617900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1443500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1359600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1493500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1389300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1300200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1624100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2174900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2612700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1745200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1706800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1837000</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4015,86 +4114,89 @@
       <c r="AH45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10356200</v>
+      </c>
+      <c r="E46" s="3">
         <v>9725800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9739200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9611400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9458400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9669300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10494900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9933500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9723100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9769900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9837100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9480300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9675900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11173900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9928500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9275400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8398900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8546300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9655400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9994800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>11823800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12216900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12185400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>11154700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8388500</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4113,86 +4215,89 @@
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2883400</v>
+      </c>
+      <c r="E47" s="3">
         <v>2873900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2880700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2762300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3274500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3806000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3259300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3059000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3045700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2861100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3324100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3293500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3310400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2825600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2530400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2850500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3525700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3402100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2354000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2515300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1532300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1104300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>467500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>402100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>412000</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4211,86 +4316,89 @@
       <c r="AH47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2228000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2629500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3033000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3388300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3565200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3578000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3530200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3494000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3103500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2811200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2761700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2462900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2189100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2073700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1877900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1704900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1477500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1275200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1272500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1387700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1388800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1322900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1154500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1089000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1018500</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4309,86 +4417,89 @@
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>783200</v>
+      </c>
+      <c r="E49" s="3">
         <v>775900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>769600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>761400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>773300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>771800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>772000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>825100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>794700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>810400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>835500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>841700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>868100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>941000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>933500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>947600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>965600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>417800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>406900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>481600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>560400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>573900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>572100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>670800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>704200</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,86 +4720,89 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>290500</v>
+      </c>
+      <c r="E52" s="3">
         <v>275900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>72300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>197100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>190900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>171600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>29800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>190800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>187300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>227900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>50700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>141900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>141700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>158800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>145500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>141400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>141200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>163800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>163100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>140100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>141900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>142300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>138400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>89400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>87600</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,86 +4922,89 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16543600</v>
+      </c>
+      <c r="E54" s="3">
         <v>16283800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16680200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16756900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17266100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17999400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18241900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17506000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16857000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16483800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16969900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16224600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>16190100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17173700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15415800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>14919800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14509000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13805200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13852000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14519400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>15447200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>15360400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>14517900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13406000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10610800</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4897,8 +5023,11 @@
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,86 +5099,87 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>817700</v>
+      </c>
+      <c r="E57" s="3">
         <v>774300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>799700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>912500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>906900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1143300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1144300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>965500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>839500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>782600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>873600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>753200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>737100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>910700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>823800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>762300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>762600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>688900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>829700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>754800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>869200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>776500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>967100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>928800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>813800</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5067,86 +5198,89 @@
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1362800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1413700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1624800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1780600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1836600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1896400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1920500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1882900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1662000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1487100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1362200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1180500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1000100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>898400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>87300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>82900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>68100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>81100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>62700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>93400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>83000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>84700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>210500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>439300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>408100</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5165,86 +5299,89 @@
       <c r="AH58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2089500</v>
+      </c>
+      <c r="E59" s="3">
         <v>1795400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2537600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1389900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1802200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2047700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2779700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1402600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1717700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1529900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2025800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1345500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1463500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1874400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3789400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3616600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3659500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3184700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3103100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3330000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3862400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4012500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3504100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3307200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3224800</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5263,86 +5400,89 @@
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6077400</v>
+      </c>
+      <c r="E60" s="3">
         <v>5951000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6063000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5985900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6381800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7271000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7226100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6151100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5969000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5782900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5573900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5204400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5082100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5645300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4700500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4461800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4490200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3954600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3995500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4178200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4814600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4873700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4681800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4675300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4446700</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5361,53 +5501,56 @@
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>755300</v>
+      </c>
+      <c r="E61" s="3">
         <v>945300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1059700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1182900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1230300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1182300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1183300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1207900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1119700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1088400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1174300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1109000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1023200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>999800</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -5424,23 +5567,23 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="X61" s="3">
         <v>1100</v>
       </c>
       <c r="Y61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Z61" s="3">
         <v>2100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>694700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>719900</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5459,8 +5602,11 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5480,7 +5626,7 @@
         <v>300</v>
       </c>
       <c r="I62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J62" s="3">
         <v>400</v>
@@ -5492,7 +5638,7 @@
         <v>400</v>
       </c>
       <c r="M62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="N62" s="3">
         <v>100</v>
@@ -5504,41 +5650,41 @@
         <v>100</v>
       </c>
       <c r="Q62" s="3">
+        <v>100</v>
+      </c>
+      <c r="R62" s="3">
         <v>980000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>891300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>752300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>601600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>597500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>652800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>656900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>648600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>536600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>501300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>465300</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,86 +6006,89 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6889800</v>
+      </c>
+      <c r="E66" s="3">
         <v>6942600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7168400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7213700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7656700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8497400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8453300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7399300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7127500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6910400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6787700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6361600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6153800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6696600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5699400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5371800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5259300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4572100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4604300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4838600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5480300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5527300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5224200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5875200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5635800</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5949,8 +6107,11 @@
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6256,11 +6424,11 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>6157000</v>
       </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
       <c r="AC70" s="3">
         <v>0</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,86 +6548,89 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>698500</v>
+      </c>
+      <c r="E72" s="3">
         <v>450600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>314100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>296300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>189800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-109200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-194900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-349300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-613500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-685600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-758100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-922400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1164400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1514800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1536600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1646700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1387000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1292300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1198200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-958100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1116800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1229800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1463300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1474300</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6475,8 +6649,11 @@
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,86 +6952,89 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9645000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9332800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9499200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9529400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9591900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9485500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9771600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10089800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9711100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9555300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10167900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9848300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10024900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10456400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9716400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9547900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9249600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9233100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9247800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9680800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9966900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9833100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9293800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7530800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-1182000</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6867,8 +7053,11 @@
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>386100</v>
+      </c>
+      <c r="E81" s="3">
         <v>182000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>105200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>181600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>117900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>78100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>167000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>260400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>59800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>94400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>158700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>180500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>399900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>53200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>99900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-259700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-85900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-128400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-250900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>159700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>152000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>110400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-40000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>14500</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-11900</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG81" s="3">
-        <v>0</v>
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,53 +7400,54 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E83" s="3">
         <v>24600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>32700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>23700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>23900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>22900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>27700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>26600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>26900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>27600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>33500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>30800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>34900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>36900</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
@@ -7273,15 +7472,15 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB83" s="3">
         <v>80200</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7294,14 +7493,17 @@
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG83" s="3">
-        <v>0</v>
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,86 +8004,89 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>973400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-213300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>273300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>119600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>115300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-546400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>712800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>320600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>564800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-292000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>285700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>268200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-27000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1110400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>373200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>277100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>413300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>116000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>176600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-164700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>143800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>355200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>153700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>473500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>743400</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7882,14 +8099,17 @@
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG89" s="3">
-        <v>0</v>
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,52 +8144,53 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3">
+      <c r="D91" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3">
         <v>-86900</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3">
         <v>-67300</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3">
         <v>-142100</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3">
         <v>-63600</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3">
         <v>-123300</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -7995,15 +8216,15 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-43800</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
@@ -8016,14 +8237,17 @@
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,86 +8445,89 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-998000</v>
+      </c>
+      <c r="E94" s="3">
         <v>726900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-159000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-132600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>232400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>866200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-276100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-74000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1119300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>178700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>523500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2100100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>283500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>812000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-138900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>532000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-984400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-591800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-486400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1558600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>160500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1653600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-780600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1023500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-357300</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
@@ -8310,14 +8540,17 @@
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG94" s="3">
-        <v>0</v>
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,52 +8585,53 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>304200</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3">
         <v>411900</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3">
         <v>402200</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3">
         <v>387800</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3">
         <v>389500</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="3">
         <v>201100</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,86 +8987,89 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-497200</v>
+      </c>
+      <c r="E100" s="3">
         <v>72900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-101300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-444400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-863000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>36000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>152100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-483100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-449000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-35000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-244500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-358400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-350000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-48300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-128800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-38300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-12900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>17900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-28000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>10200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-133700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1309900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2441100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-83900</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8836,92 +9082,95 @@
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>700</v>
+      </c>
+      <c r="E101" s="3">
         <v>4900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>25200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-6700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-20100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>22600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>5000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>6000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-21900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>25500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>5900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-21500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>23800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-30600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>12100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-72400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>28500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-206700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-120200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>17200</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC101" s="3" t="s">
         <v>3</v>
       </c>
@@ -8934,92 +9183,95 @@
       <c r="AF101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
+      <c r="AG101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-522700</v>
+      </c>
+      <c r="E102" s="3">
         <v>584700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-458800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-514500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>360600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>613900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-243200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-998600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-148800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>544700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2167700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-88600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1872100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>111400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>749300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-560200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-461800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-368400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1701000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>230100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1403700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>476400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1770900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>319400</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
@@ -9032,10 +9284,13 @@
       <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG102" s="3">
-        <v>0</v>
+      <c r="AG102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>
